--- a/docs/海克斯工坊内容总表.xlsx
+++ b/docs/海克斯工坊内容总表.xlsx
@@ -10,6 +10,7 @@
     <sheet name="海克斯(124)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="装备(44)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="锻造词条" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="世界海克斯(24)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -88,6 +89,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,27 +478,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>稀有度</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
@@ -510,27 +520,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>hex_bounty_hunter</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>悬赏猎人</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -546,27 +556,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>hex_buff_master</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>增益大师</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -582,27 +592,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>hex_chaos_king</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>混沌之王</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -618,27 +628,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>hex_colossus</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>巨像</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -654,27 +664,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>hex_death_defier</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>亡者不死</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -690,27 +700,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>hex_dragon_dance</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>龙之舞</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -726,27 +736,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>hex_dragon_feast</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>龙之盛宴</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -762,27 +772,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>hex_dragonheart</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>龙心</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -802,27 +812,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>hex_fire_warden</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>烈焰壁垒</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -838,27 +848,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>hex_firework_king</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>烟花之王</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -874,27 +884,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>hex_golden_bet</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>豪赌</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -910,27 +920,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>hex_heart_steel</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>心之钢魂</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -950,27 +960,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>hex_ice_crown</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>冰霜王冠</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -986,27 +996,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>hex_immortal_wall</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>不朽壁垒</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1022,27 +1032,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>hex_midas_hand</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>迈达斯之手</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1058,27 +1068,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>hex_mining_smelt</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>冶炼之触</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1094,27 +1104,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>hex_mining_vein</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>矿脉共鸣</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1130,27 +1140,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>hex_stack_drake</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>叠角龙</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1166,27 +1176,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>hex_stack_tank</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>坦克引擎</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1206,27 +1216,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>hex_tacz_gen_056</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>战地医疗</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1246,27 +1256,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>hex_tacz_legend</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>战地传奇</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1286,27 +1296,27 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>hex_tacz_survivor</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>弹药永续</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1322,27 +1332,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>hex_undying</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>不死鸟</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1358,27 +1368,27 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>hex_war_cry</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>战争咆哮</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -8095,4 +8105,700 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>稀有度</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>效果描述(desc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>whx_xp_friend</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>经验亲和</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>全体玩家获得的经验 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>whx_coin_tax</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>晶币税</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>全体玩家获得的晶币 -10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>whx_dmg_shortage</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>补给匮乏</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>全体玩家造成的伤害 -10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>whx_life_echo</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>生命共鸣</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>全体玩家最大生命 +4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>whx_ancient_weakness</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>远古衰弱</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>全体玩家最大生命 -6、造成伤害 -8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>whx_genesis_pact</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>创世契约</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>全体玩家经验 +20%，世界海克斯抽取消耗经验减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>whx_pasture_harmony</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>牧场丰饶</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>友好</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>友好生物移动速度 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>whx_herd_watchful</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>家畜警觉</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>友好</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>友好生物死亡时有 30% 概率不掉落战利品</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>whx_loyal_guard</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>忠诚守护</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>友好</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>友好生物攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>whx_flock_shadow</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>牧群阴影</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>友好</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>友好生物最大生命 -4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>whx_beast_king</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>万兽之王</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>友好</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>友好生物最大生命 +8、攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>whx_angel_grace</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>天使眷顾</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>友好</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>驯服生物每秒回复 0.5 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>whx_wild_spirit</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>野性难驯</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>中立生物攻击力 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>whx_vigilant_eye</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>警惕之眼</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>中立生物索敌范围 +30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>whx_pack_rage</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>兽群狂暴</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>中立生物攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>whx_hunter_eye</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>猎人之眼</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>玩家对中立生物造成的伤害 +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>whx_apex_presence</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>终焉威压</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>中立生物最大生命 +10、移速 +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>whx_peace_vision</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>和平愿景</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>玩家对中立生物造成的伤害 +30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>whx_shadow_power</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>暗影强化</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物最大生命 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>whx_fang_claw</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>尖牙利爪</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物攻击力 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>whx_predator_swift</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>捕食者迅捷</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物移动速度 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>whx_armor_shell</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>装甲外壳</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物护甲 +4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>whx_abyss_awaken</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>深渊觉醒</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物最大生命 +12、攻击力 +4、移速 +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>whx_blood_feast</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>血腥盛宴</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物最大生命 +8；击杀敌对生物获得的晶币 +50%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/海克斯工坊内容总表.xlsx
+++ b/docs/海克斯工坊内容总表.xlsx
@@ -10,7 +10,7 @@
     <sheet name="海克斯(124)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="装备(44)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="锻造词条" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="世界海克斯(24)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="世界海克斯(32)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -97,6 +97,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1404,27 +1407,27 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>hex_warden</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>守望者</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -1440,27 +1443,27 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>hex_warmaster</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>战争领主</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1480,27 +1483,27 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>hex_xp_overload</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>知识洪流</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1516,27 +1519,27 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>hex_arena_sprint</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>疾风突进</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>白银</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1552,27 +1555,27 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>hex_berserk</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>狂怒</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>白银</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>10</v>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -1588,27 +1591,27 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>hex_crit_cascade</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>暴击瀑布</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>白银</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1624,27 +1627,27 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>hex_dice_addict</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>掷骰狂人</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>白银</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1660,27 +1663,27 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>hex_duelist</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>决斗者</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>白银</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>原版</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -8113,14 +8116,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="51" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8200,7 +8203,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>全体玩家获得的晶币 -10%</t>
+          <t>全体玩家获得的晶币 -20%</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8230,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>全体玩家造成的伤害 -10%</t>
+          <t>全体玩家造成的伤害 -15%</t>
         </is>
       </c>
     </row>
@@ -8254,24 +8257,24 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>全体玩家最大生命 +4</t>
+          <t>全体玩家最大生命 +6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>whx_ancient_weakness</t>
+          <t>whx_eternal_flame</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>远古衰弱</t>
+          <t>永燃诅咒</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>棱彩</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -8281,19 +8284,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>全体玩家最大生命 -6、造成伤害 -8%</t>
+          <t>全体玩家受到的伤害 +20%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>whx_genesis_pact</t>
+          <t>whx_ancient_weakness</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>创世契约</t>
+          <t>远古衰弱</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -8308,78 +8311,78 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>全体玩家经验 +20%，世界海克斯抽取消耗经验减半</t>
+          <t>全体玩家最大生命 -10、造成伤害 -12%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>whx_pasture_harmony</t>
+          <t>whx_death_harvest</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>牧场丰饶</t>
+          <t>死亡收割</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>棱彩</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>友好</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>友好生物移动速度 +10%</t>
+          <t>全体玩家造成的伤害 -15%，死亡时损失的经验翻倍</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>whx_herd_watchful</t>
+          <t>whx_genesis_pact</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>家畜警觉</t>
+          <t>创世契约</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>棱彩</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>友好</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>友好生物死亡时有 30% 概率不掉落战利品</t>
+          <t>全体玩家经验 +30%，世界海克斯抽取消耗经验 -60%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>whx_loyal_guard</t>
+          <t>whx_pasture_harmony</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>忠诚守护</t>
+          <t>牧场丰饶</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>白银</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -8389,24 +8392,24 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>友好生物攻击力 +2</t>
+          <t>友好生物移动速度 +10%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>whx_flock_shadow</t>
+          <t>whx_herd_watchful</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>牧群阴影</t>
+          <t>家畜警觉</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>白银</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -8416,24 +8419,24 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>友好生物最大生命 -4</t>
+          <t>友好生物死亡时有 50% 概率不掉落战利品</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>whx_beast_king</t>
+          <t>whx_loyal_guard</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>万兽之王</t>
+          <t>忠诚守护</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>棱彩</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -8443,24 +8446,24 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>友好生物最大生命 +8、攻击力 +2</t>
+          <t>友好生物攻击力 +2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>whx_angel_grace</t>
+          <t>whx_flock_shadow</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>天使眷顾</t>
+          <t>牧群阴影</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>棱彩</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -8470,132 +8473,132 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>驯服生物每秒回复 0.5 点生命</t>
+          <t>友好生物最大生命 -6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>whx_wild_spirit</t>
+          <t>whx_pacifist_oath</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>野性难驯</t>
+          <t>和平契约</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>中立</t>
+          <t>友好</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>中立生物攻击力 +1</t>
+          <t>友好生物死亡时 100% 不掉落任何战利品</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>whx_vigilant_eye</t>
+          <t>whx_beast_king</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>警惕之眼</t>
+          <t>万兽之王</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>棱彩</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>中立</t>
+          <t>友好</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>中立生物索敌范围 +30%</t>
+          <t>友好生物最大生命 +8、攻击力 +2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>whx_pack_rage</t>
+          <t>whx_angel_grace</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>兽群狂暴</t>
+          <t>天使眷顾</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>棱彩</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>中立</t>
+          <t>友好</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>中立生物攻击力 +2</t>
+          <t>驯服生物每秒回复 1.0 点生命</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>whx_hunter_eye</t>
+          <t>whx_wrath_of_fields</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>猎人之眼</t>
+          <t>田野之怒</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>棱彩</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>中立</t>
+          <t>友好</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>玩家对中立生物造成的伤害 +15%</t>
+          <t>友好生物受到攻击时 100% 获得力量与速度反扑（5 秒）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>whx_apex_presence</t>
+          <t>whx_wild_spirit</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>终焉威压</t>
+          <t>野性难驯</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>棱彩</t>
+          <t>白银</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -8605,24 +8608,24 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>中立生物最大生命 +10、移速 +15%</t>
+          <t>中立生物攻击力 +2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>whx_peace_vision</t>
+          <t>whx_vigilant_eye</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>和平愿景</t>
+          <t>警惕之眼</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>棱彩</t>
+          <t>白银</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -8632,73 +8635,73 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>玩家对中立生物造成的伤害 +30%</t>
+          <t>中立生物索敌范围 +45%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>whx_shadow_power</t>
+          <t>whx_pack_rage</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>暗影强化</t>
+          <t>兽群狂暴</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>敌对</t>
+          <t>中立</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>敌对生物最大生命 +2</t>
+          <t>中立生物攻击力 +3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>whx_fang_claw</t>
+          <t>whx_hunter_eye</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>尖牙利爪</t>
+          <t>猎人之眼</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>敌对</t>
+          <t>中立</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>敌对生物攻击力 +1</t>
+          <t>玩家对中立生物造成的伤害 +20%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>whx_predator_swift</t>
+          <t>whx_wild_instinct</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>捕食者迅捷</t>
+          <t>野性本能</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8708,51 +8711,51 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>敌对</t>
+          <t>中立</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>敌对生物移动速度 +20%</t>
+          <t>中立生物受到攻击时 50% 概率获得力量与速度反击（5 秒）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>whx_armor_shell</t>
+          <t>whx_apex_presence</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>装甲外壳</t>
+          <t>终焉威压</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>棱彩</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>敌对</t>
+          <t>中立</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>敌对生物护甲 +4</t>
+          <t>中立生物最大生命 +16、移速 +25%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>whx_abyss_awaken</t>
+          <t>whx_peace_vision</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>深渊觉醒</t>
+          <t>和平愿景</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8762,39 +8765,255 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>敌对</t>
+          <t>中立</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>敌对生物最大生命 +12、攻击力 +4、移速 +15%</t>
+          <t>玩家对中立生物造成的伤害 +40%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t>whx_neutral_dominion</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>中立统御</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>中立生物最大生命 +6、攻击力 +4，玩家对中立生物造成的伤害 -30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>whx_shadow_power</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>暗影强化</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物最大生命 +4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>whx_fang_claw</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>尖牙利爪</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>whx_predator_swift</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>捕食者迅捷</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物移动速度 +30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>whx_armor_shell</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>装甲外壳</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物护甲 +6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>whx_undead_march</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>亡灵行军</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物死亡时 25% 概率在原地召唤 1 只同类</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>whx_abyss_awaken</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>深渊觉醒</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物最大生命 +20、攻击力 +6、移速 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>whx_blood_feast</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>血腥盛宴</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>棱彩</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>敌对</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>敌对生物最大生命 +8；击杀敌对生物获得的晶币 +50%</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物最大生命 +12；击杀敌对生物获得的晶币 +75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>whx_demon_contract</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>恶魔契约</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>敌对生物攻击吸血 30%，25% 概率对玩家施加虚弱与缓慢（5 秒）</t>
         </is>
       </c>
     </row>

--- a/docs/海克斯工坊内容总表.xlsx
+++ b/docs/海克斯工坊内容总表.xlsx
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>全体玩家获得的经验 +10%</t>
+          <t>全体玩家获得的经验 +15%</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>全体玩家获得的晶币 -20%</t>
+          <t>全体玩家获得的晶币 -30%</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>全体玩家造成的伤害 -15%</t>
+          <t>全体玩家造成的伤害 -25%</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>全体玩家最大生命 +6</t>
+          <t>全体玩家最大生命 +10</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>全体玩家受到的伤害 +20%</t>
+          <t>全体玩家受到的伤害 +30%</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>全体玩家最大生命 -10、造成伤害 -12%</t>
+          <t>全体玩家最大生命 -15、造成伤害 -18%</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>全体玩家造成的伤害 -15%，死亡时损失的经验翻倍</t>
+          <t>全体玩家造成的伤害 -25%，死亡时损失的经验为原来的 2.5 倍</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>全体玩家经验 +30%，世界海克斯抽取消耗经验 -60%</t>
+          <t>全体玩家经验 +50%，世界海克斯抽取消耗经验 -60%</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>友好生物移动速度 +10%</t>
+          <t>友好生物移动速度 +15%</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>友好生物死亡时有 50% 概率不掉落战利品</t>
+          <t>友好生物死亡时有 75% 概率不掉落战利品</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>友好生物攻击力 +2</t>
+          <t>友好生物攻击力 +3</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>友好生物最大生命 -6</t>
+          <t>友好生物最大生命 -10</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>友好生物最大生命 +8、攻击力 +2</t>
+          <t>友好生物最大生命 +14、攻击力 +4</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>驯服生物每秒回复 1.0 点生命</t>
+          <t>驯服生物每秒回复 1.5 点生命</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>友好生物受到攻击时 100% 获得力量与速度反扑（5 秒）</t>
+          <t>友好生物受到攻击时 100% 获得力量与速度反扑（7 秒）</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>中立生物攻击力 +2</t>
+          <t>中立生物攻击力 +3</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>中立生物索敌范围 +45%</t>
+          <t>中立生物索敌范围 +60%</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>中立生物攻击力 +3</t>
+          <t>中立生物攻击力 +4.5</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>玩家对中立生物造成的伤害 +20%</t>
+          <t>玩家对中立生物造成的伤害 +30%</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>中立生物受到攻击时 50% 概率获得力量与速度反击（5 秒）</t>
+          <t>中立生物受到攻击时 75% 概率获得力量与速度反击（7 秒）</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>中立生物最大生命 +16、移速 +25%</t>
+          <t>中立生物最大生命 +24、移速 +40%</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>玩家对中立生物造成的伤害 +40%</t>
+          <t>玩家对中立生物造成的伤害 +55%</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>中立生物最大生命 +6、攻击力 +4，玩家对中立生物造成的伤害 -30%</t>
+          <t>中立生物最大生命 +10、攻击力 +6，玩家对中立生物造成的伤害 -45%</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>敌对生物最大生命 +4</t>
+          <t>敌对生物最大生命 +6</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>敌对生物攻击力 +2</t>
+          <t>敌对生物攻击力 +3</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>敌对生物移动速度 +30%</t>
+          <t>敌对生物移动速度 +45%</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>敌对生物护甲 +6</t>
+          <t>敌对生物护甲 +9</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>敌对生物死亡时 25% 概率在原地召唤 1 只同类</t>
+          <t>敌对生物死亡时 40% 概率在原地召唤 1 只同类</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>敌对生物最大生命 +20、攻击力 +6、移速 +25%</t>
+          <t>敌对生物最大生命 +30、攻击力 +9、移速 +40%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>敌对生物最大生命 +12；击杀敌对生物获得的晶币 +75%</t>
+          <t>敌对生物最大生命 +18；击杀敌对生物获得的晶币 +100%</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>敌对生物攻击吸血 30%，25% 概率对玩家施加虚弱与缓慢（5 秒）</t>
+          <t>敌对生物攻击吸血 40%，40% 概率对玩家施加虚弱与缓慢（7 秒）</t>
         </is>
       </c>
     </row>

--- a/docs/海克斯工坊内容总表.xlsx
+++ b/docs/海克斯工坊内容总表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="海克斯(124)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="海克斯(145)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="装备(44)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="锻造词条" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="世界海克斯(32)" sheetId="4" state="visible" r:id="rId4"/>
@@ -61,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -69,11 +69,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -100,6 +114,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -467,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5051,6 +5068,726 @@
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>每级造成伤害回复 10%；击杀回复 2 生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>hex_end_void_walker</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>虚空行者</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>end_fall_reduce:0.8</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>在末地时摔落伤害减少 80%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>hex_end_dragon_slayer</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>灭龙之志</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>end_damage:0.3</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>在末地时攻击伤害提升 30%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>hex_end_pearl_master</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>珍珠掌控</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>end_crit:0.15</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>在末地时暴击率提升 15%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>hex_end_void_protect</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>虚空庇护</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>end_void_reduce:0.9</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>在末地时虚空（掉出世界）伤害减少 90%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>hex_nether_fire_lord</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>火焰领主</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>nether_fire_reduce:0.7</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="n"/>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>在下界时火焰伤害减少 70%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>hex_nether_lava_walker</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>熔岩行者</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>nether_lava_reduce:0.9,nether_fire_reduce:0.5</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="n"/>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>在下界时岩浆伤害减少 90%、火焰伤害减少 50%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>hex_nether_demon_hunter</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>恶魔猎手</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>nether_damage:0.3</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="inlineStr">
+        <is>
+          <t>在下界时攻击伤害提升 30%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>hex_nether_gold_greed</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>下界贪欲</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>nether_coin:0.5</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>在下界时击杀获得的晶币提升 50%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>hex_combo_vamp</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>连环吸血</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>lifesteal:0.06,melee_power:0.1</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>吸血 6% 并提升近战伤害 10%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>hex_crit_leech</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>暴击吮血</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>crit:0.1,lifesteal:0.04</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>暴击率提升 10%，并将伤害的 4% 转化为生命（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>hex_execute_haste</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>处决滚雪球</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>execute:0.15,xp_bonus:0.2</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>斩杀线提升 15%，击杀经验获取提升 20%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>hex_thorn_shell</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>荆棘护壳</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>thorns:5,last_stand:0.15</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>反弹 5 点伤害，生命低于 30% 时再减伤 15%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>hex_blood_rampage</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>血怒狂暴</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>vamp_rage:0.15,rampage:0.2</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>生命低于 50% 时吸血翻倍至 15%，击杀后进入狂暴（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>hex_frost_crit</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>霜暴连击</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>crit:0.12,crit_damage:0.5</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="inlineStr">
+        <is>
+          <t>暴击率提升 12%，暴击伤害提升 50%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>hex_arcane_vamp</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>奥术吸血鬼</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>lifesteal:0.08,arcane_shield:0.25</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>吸血 8%，并受到魔法伤害时减免 25%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>hex_loot_coin</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>掠夺双收</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
+        <is>
+          <t>loot_bonus:0.3,coin_bonus:0.3</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>生物掉落数量提升 30%，击杀晶币提升 30%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>hex_blood_artist</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>血艺大师</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>lifesteal:0.12,overshield:0.3,kill_heal:1.5</t>
+        </is>
+      </c>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="inlineStr">
+        <is>
+          <t>吸血 12%、溢出治疗转护盾 30%、击杀回血 1.5（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>hex_death_dance</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>死亡之舞</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>death_defy:0.25,last_stand:0.3</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t>致命伤害有 25% 概率免疫并回血，生命低于 30% 时减伤 30%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>hex_executioner</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>行刑官</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>execute:0.2,melee_power:0.15,lifesteal:0.08</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t>斩杀线提升 20%、近战伤害提升 15%、吸血 8%（每级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>hex_dragon_coin</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>龙晶掠夺者</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>棱彩</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>原版</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>coin_bonus:0.4,xp_bonus:0.3,loot_double:1</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>击杀晶币提升 40%、经验提升 30%、掉落数量翻倍（每级）</t>
         </is>
       </c>
     </row>
